--- a/decks/blank-slate/keyword-research.xlsx
+++ b/decks/blank-slate/keyword-research.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected. Commercial intent — direct buyer query</t>
+          <t>Easy win: fast indexing expected. Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected. Commercial intent — direct buyer query</t>
+          <t>Easy win: fast indexing expected. Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected. Commercial intent — direct buyer query</t>
+          <t>Easy win: fast indexing expected. Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected. Commercial intent — direct buyer query</t>
+          <t>Easy win: fast indexing expected. Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected. Commercial intent — direct buyer query</t>
+          <t>Easy win: fast indexing expected. Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Keeping Staff Training on Track — and Retained</t>
+          <t>Keeping Staff Training on Track and Retained</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected. Commercial intent — direct buyer query</t>
+          <t>Easy win: fast indexing expected. Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Easy win — fast indexing expected</t>
+          <t>Easy win: fast indexing expected</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>Pillar anchor — highest volume in Compliance &amp; Safety Readiness</t>
+          <t>Pillar anchor: highest volume in Compliance &amp; Safety Readiness</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>Pillar anchor — highest volume in Engagement &amp; Adoption</t>
+          <t>Pillar anchor: highest volume in Engagement &amp; Adoption</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>Pillar anchor — highest volume in Microlearning &amp; Delivery</t>
+          <t>Pillar anchor: highest volume in Microlearning &amp; Delivery</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>Pillar anchor — highest volume in Knowledge Retention &amp; the Science of Remembering</t>
+          <t>Pillar anchor: highest volume in Knowledge Retention &amp; the Science of Remembering</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>Pillar anchor — highest volume in Workforce Training &amp; Readiness Measurement</t>
+          <t>Pillar anchor: highest volume in Workforce Training &amp; Readiness Measurement</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>Commercial intent — direct buyer query</t>
+          <t>Commercial intent: direct buyer query</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -13355,7 +13355,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -15533,7 +15533,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -16952,7 +16952,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -17183,7 +17183,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -17414,7 +17414,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -17579,7 +17579,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -18305,7 +18305,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -18635,7 +18635,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -19064,7 +19064,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -19229,7 +19229,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -19988,7 +19988,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -20219,7 +20219,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -20483,7 +20483,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -20978,7 +20978,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -21737,7 +21737,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -21935,7 +21935,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -22232,7 +22232,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -22298,7 +22298,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -22595,7 +22595,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -22661,7 +22661,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -23057,7 +23057,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -23090,7 +23090,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -23519,7 +23519,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -23651,7 +23651,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -23717,7 +23717,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -24179,7 +24179,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -24245,7 +24245,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -24311,7 +24311,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
@@ -24410,7 +24410,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
@@ -24443,7 +24443,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
@@ -24575,7 +24575,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
@@ -24872,7 +24872,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
@@ -25103,7 +25103,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
@@ -25202,7 +25202,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
@@ -25235,7 +25235,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -25268,7 +25268,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -25301,7 +25301,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -25598,7 +25598,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -26225,7 +26225,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
@@ -26258,7 +26258,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
@@ -26390,7 +26390,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
@@ -26621,7 +26621,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
@@ -26720,7 +26720,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
@@ -26753,7 +26753,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
@@ -26885,7 +26885,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
@@ -26951,7 +26951,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
@@ -27083,7 +27083,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
@@ -27116,7 +27116,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
@@ -27182,7 +27182,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
@@ -27413,7 +27413,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
@@ -27446,7 +27446,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
@@ -27479,7 +27479,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
@@ -27578,7 +27578,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
@@ -27644,7 +27644,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -28172,7 +28172,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
@@ -28205,7 +28205,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -28238,7 +28238,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -28337,7 +28337,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
@@ -28403,7 +28403,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
@@ -28436,7 +28436,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
@@ -28502,7 +28502,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
@@ -28601,7 +28601,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
@@ -28667,7 +28667,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
@@ -28700,7 +28700,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
@@ -28865,7 +28865,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
@@ -28898,7 +28898,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
@@ -29030,7 +29030,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
@@ -29063,7 +29063,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -29096,7 +29096,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
@@ -29591,7 +29591,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
@@ -29657,7 +29657,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
@@ -29855,7 +29855,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
@@ -29888,7 +29888,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
@@ -29921,7 +29921,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
@@ -30119,7 +30119,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
@@ -30152,7 +30152,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
@@ -30185,7 +30185,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
@@ -30284,7 +30284,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
@@ -30350,7 +30350,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
@@ -30383,7 +30383,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
@@ -30416,7 +30416,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
@@ -30449,7 +30449,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
@@ -30482,7 +30482,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
@@ -30548,7 +30548,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
@@ -30581,7 +30581,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
@@ -30614,7 +30614,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
@@ -30647,7 +30647,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
@@ -30713,7 +30713,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
@@ -30812,7 +30812,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
@@ -30878,7 +30878,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
@@ -31340,7 +31340,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
@@ -31637,7 +31637,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
@@ -31670,7 +31670,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
@@ -31703,7 +31703,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
@@ -32363,7 +32363,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
@@ -32792,7 +32792,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F795" t="inlineStr">
@@ -32825,7 +32825,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
@@ -32858,7 +32858,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
@@ -32924,7 +32924,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F799" t="inlineStr">
@@ -33089,7 +33089,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
@@ -33155,7 +33155,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
@@ -33320,7 +33320,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
@@ -33485,7 +33485,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F816" t="inlineStr">
@@ -33518,7 +33518,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
@@ -33551,7 +33551,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
@@ -33584,7 +33584,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
@@ -33617,7 +33617,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
@@ -33650,7 +33650,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
@@ -33716,7 +33716,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -33980,7 +33980,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
@@ -34145,7 +34145,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -34178,7 +34178,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -34211,7 +34211,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -34277,7 +34277,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -34310,7 +34310,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
@@ -34772,7 +34772,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
@@ -34805,7 +34805,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
@@ -34871,7 +34871,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
@@ -34937,7 +34937,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
@@ -34970,7 +34970,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
@@ -35003,7 +35003,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
@@ -35069,7 +35069,7 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
@@ -35102,7 +35102,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
@@ -35234,7 +35234,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
@@ -35267,7 +35267,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
@@ -35300,7 +35300,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
@@ -35333,7 +35333,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
@@ -35399,7 +35399,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
@@ -35432,7 +35432,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F875" t="inlineStr">
@@ -35465,7 +35465,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
@@ -35498,7 +35498,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F877" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
@@ -35564,7 +35564,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F879" t="inlineStr">
@@ -35597,7 +35597,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
@@ -35630,7 +35630,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
@@ -35663,7 +35663,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
@@ -35696,7 +35696,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
@@ -35729,7 +35729,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
@@ -35762,7 +35762,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
@@ -35795,7 +35795,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
@@ -35828,7 +35828,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
@@ -35861,7 +35861,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
@@ -35927,7 +35927,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
@@ -35960,7 +35960,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
@@ -35993,7 +35993,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
@@ -36026,7 +36026,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F894" t="inlineStr">
@@ -36092,7 +36092,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
@@ -36125,7 +36125,7 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
@@ -36158,7 +36158,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
@@ -36191,7 +36191,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36394,7 +36394,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36417,7 +36417,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36463,7 +36463,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36647,7 +36647,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36670,7 +36670,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36785,7 +36785,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36808,7 +36808,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36854,7 +36854,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -36877,7 +36877,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Branded queries for a competitor — the searcher already knows the brand they want. Impossible to outrank a brand for its own name.</t>
+          <t>Branded queries for a competitor, the searcher already knows the brand they want. Impossible to outrank a brand for its own name.</t>
         </is>
       </c>
     </row>
@@ -36992,7 +36992,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37176,7 +37176,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37222,7 +37222,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37291,7 +37291,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37452,7 +37452,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37475,7 +37475,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Branded queries for a competitor — the searcher already knows the brand they want. Impossible to outrank a brand for its own name.</t>
+          <t>Branded queries for a competitor, the searcher already knows the brand they want. Impossible to outrank a brand for its own name.</t>
         </is>
       </c>
     </row>
@@ -37567,7 +37567,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37590,7 +37590,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37613,7 +37613,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37636,7 +37636,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37705,7 +37705,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37774,7 +37774,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37912,7 +37912,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37935,7 +37935,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -37958,7 +37958,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38073,7 +38073,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38142,7 +38142,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38257,7 +38257,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38280,7 +38280,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38303,7 +38303,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38395,7 +38395,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>The commodity category the brand rule says not to sound like. Not excluded forever — captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
+          <t>The commodity category the brand rule says not to sound like. Not excluded forever: captured later with a differentiated, retention-first angle (see the Category Prize slide), not a me-too LMS page.</t>
         </is>
       </c>
     </row>
@@ -38442,7 +38442,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Blank Slate — Keyword Research Workbook</t>
+          <t>Blank Slate: Keyword Research Workbook</t>
         </is>
       </c>
     </row>
@@ -38464,9 +38464,9 @@
       <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Three working sheets:
-  1. Article Plan     — the 120 articles in the 3-month plan, mapped to month, pillar, and funnel stage. Titles are working headlines; the keyword, angle, and funnel stage are the locked commitment.
-  2. Keyword Universe — the broader on-brand research from SEMrush; planned keywords are flagged 'Yes (planned)', the rest are overflow for future months.
-  3. Excluded         — high-volume keywords intentionally left out of the core plan, with the reason for each.</t>
+  1. Article Plan     - the 120 articles in the 3-month plan, mapped to month, pillar, and funnel stage. Titles are working headlines; the keyword, angle, and funnel stage are the locked commitment.
+  2. Keyword Universe, the broader on-brand research from SEMrush; planned keywords are flagged 'Yes (planned)', the rest are overflow for future months.
+  3. Excluded         - high-volume keywords intentionally left out of the core plan, with the reason for each.</t>
         </is>
       </c>
     </row>
@@ -38480,11 +38480,11 @@
     <row r="8" ht="82" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Monthly Searches — US monthly search volume (SEMrush)
-  KD               — keyword difficulty (0–100). Bands: 0–20 Very Easy, 21–35 Easy, 36–50 Moderate, 51+ Hard
-  Pillar           — content cluster the keyword belongs to (color-coded)
-  Intent           — Info (educational), Compare (research), Decision (ready to buy)
-  Funnel           — Top (awareness), Middle (consideration), Bottom (action)</t>
+          <t xml:space="preserve">  Monthly Searches, US monthly search volume (SEMrush)
+  KD               - keyword difficulty (0–100). Bands: 0–20 Very Easy, 21–35 Easy, 36–50 Moderate, 51+ Hard
+  Pillar           - content cluster the keyword belongs to (color-coded)
+  Intent           - Info (educational), Compare (research), Decision (ready to buy)
+  Funnel           - Top (awareness), Middle (consideration), Bottom (action)</t>
         </is>
       </c>
     </row>
@@ -38498,11 +38498,11 @@
     <row r="11" ht="82" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Knowledge Retention &amp; the Science of Remembering — the mechanism and your credibility engine. Spaced repetition, the forgetting curve, knowledge retention: the science that makes your proof believable.
-  Compliance &amp; Safety Readiness — your highest-intent commercial vertical. Compliance and safety training that must stick, where 'proves retention, not attendance' lands hardest.
-  Microlearning &amp; Delivery — the format buyers search for. You own it with a readiness-first frame instead of a feature list.
-  Engagement &amp; Adoption — answers the 'my team won't use it' objection with the time-burden proof.
-  Workforce Training &amp; Readiness Measurement — the True Knowledge Analytics angle: measuring readiness, tracking training, frontline leadership.</t>
+          <t xml:space="preserve">  Knowledge Retention &amp; the Science of Remembering, the mechanism and your credibility engine. Spaced repetition, the forgetting curve, knowledge retention: the science that makes your proof believable.
+  Compliance &amp; Safety Readiness, your highest-intent commercial vertical. Compliance and safety training that must stick, where 'proves retention, not attendance' lands hardest.
+  Microlearning &amp; Delivery, the format buyers search for. You own it with a readiness-first frame instead of a feature list.
+  Engagement &amp; Adoption: answers the 'my team won't use it' objection with the time-burden proof.
+  Workforce Training &amp; Readiness Measurement, the True Knowledge Analytics angle: measuring readiness, tracking training, frontline leadership.</t>
         </is>
       </c>
     </row>
@@ -38517,7 +38517,7 @@
       <c r="A14" s="21" t="inlineStr">
         <is>
           <t>The plan runs roughly 8% awareness / 66% consideration / 26% decision.
-Weighted toward the middle of the funnel — the 'how do I fix retention' searches where buyers compare approaches and Blank Slate's proof does the most work.
+Weighted toward the middle of the funnel, the 'how do I fix retention' searches where buyers compare approaches and Blank Slate's proof does the most work.
 The plan is deliberately on-brand: it never positions Blank Slate as an LMS, e-learning, or 'training software'.</t>
         </is>
       </c>
@@ -38533,11 +38533,11 @@
       <c r="A17" s="21" t="inlineStr">
         <is>
           <t>See the 'Excluded' sheet. The big categories:
-  LMS / e-learning — the commodity category. Deferred, not dropped: it gets a differentiated, retention-first angle later, not a me-too page.
-  Consumer / language-learning (Anki, vocabulary, study apps) — high volume, wrong buyer.
-  HR-process / fitness noise (performance-improvement plans, personal trainers) — shares words, not intent.
-  Navigational employee-portal logins (Kroger, Marriott) — competitors accidentally rank; zero value here.
-  Competitor-branded queries (Axonify, Cerego, Qstream, Area9) — impossible to outrank a brand for its own name.</t>
+  LMS / e-learning, the commodity category. Deferred, not dropped: it gets a differentiated, retention-first angle later, not a me-too page.
+  Consumer / language-learning (Anki, vocabulary, study apps) - high volume, wrong buyer.
+  HR-process / fitness noise (performance-improvement plans, personal trainers) - shares words, not intent.
+  Navigational employee-portal logins (Kroger, Marriott) - competitors accidentally rank; zero value here.
+  Competitor-branded queries (Axonify, Cerego, Qstream, Area9) - impossible to outrank a brand for its own name.</t>
         </is>
       </c>
     </row>
@@ -38552,8 +38552,8 @@
       <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Approve the 120-article plan and ClusterMagic begins the Month 1 batch within 5 business days.
-Articles are 1,200–2,000 words, expert-edited, internally linked, and schema-marked — shipped as drafts for your review.
-Month 1 also fixes the technical foundation (H1s, unique titles, Organization + Article schema) — the fastest ranking and AI-citation unlock.</t>
+Articles are 1,200–2,000 words, expert-edited, internally linked, and schema-marked: shipped as drafts for your review.
+Month 1 also fixes the technical foundation (H1s, unique titles, Organization + Article schema) - the fastest ranking and AI-citation unlock.</t>
         </is>
       </c>
     </row>
